--- a/templates/견적서_template.xlsx
+++ b/templates/견적서_template.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DAILYCIGAR_DB\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87826DEB-33BD-4B93-B3D8-1F29397344D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96847785-3CDA-4C97-A7EF-94FB127C953A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서_기본" sheetId="1" r:id="rId1"/>
+    <sheet name="시가 외" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">견적서_기본!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'시가 외'!$1:$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>견 적 서</t>
   </si>
@@ -932,97 +934,97 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="13" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="31" fontId="11" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="31" fontId="11" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="13" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="17">
     <cellStyle name="쉼표 [0]" xfId="13" builtinId="6"/>
@@ -1094,6 +1096,58 @@
         <a:xfrm>
           <a:off x="0" y="707814"/>
           <a:ext cx="1092200" cy="1096433"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>115147</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>93980</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{453FCA82-2303-4317-9830-467B49EAB4D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="709507"/>
+          <a:ext cx="1092200" cy="1098973"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1386,126 +1440,126 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
     </row>
     <row r="2" spans="1:9" ht="6.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="74"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
+      <c r="A2" s="49"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="44">
+      <c r="A3" s="72">
         <f ca="1">TODAY()</f>
         <v>46110</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="41" t="s">
+      <c r="B3" s="73"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47" t="s">
+      <c r="F3" s="48"/>
+      <c r="G3" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="45"/>
-      <c r="I3" s="48"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="75"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="26"/>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="42"/>
+      <c r="D4" s="70"/>
       <c r="E4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="56"/>
-      <c r="G4" s="35" t="s">
+      <c r="F4" s="60"/>
+      <c r="G4" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="36"/>
-      <c r="I4" s="37"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="59"/>
     </row>
     <row r="5" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="35" t="s">
+      <c r="C5" s="81"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="36"/>
-      <c r="I5" s="37"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="59"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="14"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="70"/>
       <c r="E6" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="81"/>
-      <c r="G6" s="35" t="s">
+      <c r="F6" s="56"/>
+      <c r="G6" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="37"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="59"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="15"/>
       <c r="B7" s="16"/>
       <c r="C7" s="17"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="49" t="s">
+      <c r="D7" s="71"/>
+      <c r="E7" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="72" t="s">
+      <c r="F7" s="65"/>
+      <c r="G7" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="60"/>
-      <c r="I7" s="61"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="46"/>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
       <c r="D8" s="32"/>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="71"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="43"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
+      <c r="B9" s="73"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="48"/>
       <c r="E9" s="21" t="s">
         <v>12</v>
       </c>
@@ -1523,12 +1577,12 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
       <c r="E10" s="30"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -1536,7 +1590,7 @@
       <c r="I10" s="31"/>
     </row>
     <row r="11" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="79"/>
+      <c r="A11" s="54"/>
       <c r="B11" s="33"/>
       <c r="C11" s="34"/>
       <c r="D11" s="34"/>
@@ -1547,7 +1601,7 @@
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="79"/>
+      <c r="A12" s="54"/>
       <c r="B12" s="33"/>
       <c r="C12" s="34"/>
       <c r="D12" s="34"/>
@@ -1558,7 +1612,7 @@
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="79"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="33"/>
       <c r="C13" s="34"/>
       <c r="D13" s="34"/>
@@ -1569,7 +1623,7 @@
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="79"/>
+      <c r="A14" s="54"/>
       <c r="B14" s="33"/>
       <c r="C14" s="34"/>
       <c r="D14" s="34"/>
@@ -1580,7 +1634,7 @@
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="79"/>
+      <c r="A15" s="54"/>
       <c r="B15" s="38"/>
       <c r="C15" s="34"/>
       <c r="D15" s="34"/>
@@ -1591,7 +1645,7 @@
       <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="79"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="38"/>
       <c r="C16" s="34"/>
       <c r="D16" s="34"/>
@@ -1602,7 +1656,7 @@
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="79"/>
+      <c r="A17" s="54"/>
       <c r="B17" s="38"/>
       <c r="C17" s="34"/>
       <c r="D17" s="34"/>
@@ -1613,7 +1667,7 @@
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="79"/>
+      <c r="A18" s="54"/>
       <c r="B18" s="38"/>
       <c r="C18" s="34"/>
       <c r="D18" s="34"/>
@@ -1624,7 +1678,7 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="79"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="38"/>
       <c r="C19" s="34"/>
       <c r="D19" s="34"/>
@@ -1635,7 +1689,7 @@
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="79"/>
+      <c r="A20" s="54"/>
       <c r="B20" s="38"/>
       <c r="C20" s="34"/>
       <c r="D20" s="34"/>
@@ -1646,7 +1700,7 @@
       <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="79"/>
+      <c r="A21" s="54"/>
       <c r="B21" s="38"/>
       <c r="C21" s="34"/>
       <c r="D21" s="34"/>
@@ -1657,7 +1711,7 @@
       <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="79"/>
+      <c r="A22" s="54"/>
       <c r="B22" s="38"/>
       <c r="C22" s="34"/>
       <c r="D22" s="34"/>
@@ -1668,7 +1722,7 @@
       <c r="I22" s="7"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="79"/>
+      <c r="A23" s="54"/>
       <c r="B23" s="38"/>
       <c r="C23" s="34"/>
       <c r="D23" s="34"/>
@@ -1679,7 +1733,7 @@
       <c r="I23" s="7"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="79"/>
+      <c r="A24" s="54"/>
       <c r="B24" s="38"/>
       <c r="C24" s="34"/>
       <c r="D24" s="34"/>
@@ -1690,7 +1744,7 @@
       <c r="I24" s="7"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="79"/>
+      <c r="A25" s="54"/>
       <c r="B25" s="38"/>
       <c r="C25" s="34"/>
       <c r="D25" s="34"/>
@@ -1701,7 +1755,7 @@
       <c r="I25" s="7"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="79"/>
+      <c r="A26" s="54"/>
       <c r="B26" s="38"/>
       <c r="C26" s="34"/>
       <c r="D26" s="34"/>
@@ -1712,7 +1766,7 @@
       <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="79"/>
+      <c r="A27" s="54"/>
       <c r="B27" s="33"/>
       <c r="C27" s="34"/>
       <c r="D27" s="34"/>
@@ -1723,7 +1777,7 @@
       <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="79"/>
+      <c r="A28" s="54"/>
       <c r="B28" s="33"/>
       <c r="C28" s="34"/>
       <c r="D28" s="34"/>
@@ -1734,7 +1788,7 @@
       <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="79"/>
+      <c r="A29" s="54"/>
       <c r="B29" s="33"/>
       <c r="C29" s="34"/>
       <c r="D29" s="34"/>
@@ -1745,7 +1799,7 @@
       <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="79"/>
+      <c r="A30" s="54"/>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
       <c r="D30" s="34"/>
@@ -1756,7 +1810,7 @@
       <c r="I30" s="7"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="79"/>
+      <c r="A31" s="54"/>
       <c r="B31" s="33"/>
       <c r="C31" s="34"/>
       <c r="D31" s="34"/>
@@ -1767,7 +1821,7 @@
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="79"/>
+      <c r="A32" s="54"/>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
       <c r="D32" s="34"/>
@@ -1778,7 +1832,7 @@
       <c r="I32" s="7"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A33" s="79"/>
+      <c r="A33" s="54"/>
       <c r="B33" s="33"/>
       <c r="C33" s="34"/>
       <c r="D33" s="34"/>
@@ -1789,7 +1843,7 @@
       <c r="I33" s="7"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="79"/>
+      <c r="A34" s="54"/>
       <c r="B34" s="33"/>
       <c r="C34" s="34"/>
       <c r="D34" s="34"/>
@@ -1800,7 +1854,7 @@
       <c r="I34" s="7"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A35" s="79"/>
+      <c r="A35" s="54"/>
       <c r="B35" s="33"/>
       <c r="C35" s="34"/>
       <c r="D35" s="34"/>
@@ -1811,7 +1865,7 @@
       <c r="I35" s="7"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A36" s="79"/>
+      <c r="A36" s="54"/>
       <c r="B36" s="33"/>
       <c r="C36" s="34"/>
       <c r="D36" s="34"/>
@@ -1822,7 +1876,7 @@
       <c r="I36" s="7"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A37" s="79"/>
+      <c r="A37" s="54"/>
       <c r="B37" s="33"/>
       <c r="C37" s="34"/>
       <c r="D37" s="34"/>
@@ -1833,7 +1887,7 @@
       <c r="I37" s="7"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="79"/>
+      <c r="A38" s="54"/>
       <c r="B38" s="33"/>
       <c r="C38" s="34"/>
       <c r="D38" s="34"/>
@@ -1844,7 +1898,7 @@
       <c r="I38" s="7"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="79"/>
+      <c r="A39" s="54"/>
       <c r="B39" s="33"/>
       <c r="C39" s="34"/>
       <c r="D39" s="34"/>
@@ -1855,7 +1909,7 @@
       <c r="I39" s="7"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A40" s="79"/>
+      <c r="A40" s="54"/>
       <c r="B40" s="33"/>
       <c r="C40" s="34"/>
       <c r="D40" s="34"/>
@@ -1866,7 +1920,7 @@
       <c r="I40" s="7"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A41" s="79"/>
+      <c r="A41" s="54"/>
       <c r="B41" s="33"/>
       <c r="C41" s="34"/>
       <c r="D41" s="34"/>
@@ -1877,7 +1931,7 @@
       <c r="I41" s="7"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A42" s="79"/>
+      <c r="A42" s="54"/>
       <c r="B42" s="33"/>
       <c r="C42" s="34"/>
       <c r="D42" s="34"/>
@@ -1888,7 +1942,7 @@
       <c r="I42" s="7"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A43" s="79"/>
+      <c r="A43" s="54"/>
       <c r="B43" s="33"/>
       <c r="C43" s="34"/>
       <c r="D43" s="34"/>
@@ -1899,7 +1953,7 @@
       <c r="I43" s="7"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A44" s="79"/>
+      <c r="A44" s="54"/>
       <c r="B44" s="33"/>
       <c r="C44" s="34"/>
       <c r="D44" s="34"/>
@@ -1910,7 +1964,7 @@
       <c r="I44" s="7"/>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="79"/>
+      <c r="A45" s="54"/>
       <c r="B45" s="38"/>
       <c r="C45" s="34"/>
       <c r="D45" s="34"/>
@@ -1921,7 +1975,7 @@
       <c r="I45" s="7"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A46" s="79"/>
+      <c r="A46" s="54"/>
       <c r="B46" s="38"/>
       <c r="C46" s="34"/>
       <c r="D46" s="34"/>
@@ -1932,7 +1986,7 @@
       <c r="I46" s="7"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A47" s="79"/>
+      <c r="A47" s="54"/>
       <c r="B47" s="38"/>
       <c r="C47" s="34"/>
       <c r="D47" s="34"/>
@@ -1943,7 +1997,7 @@
       <c r="I47" s="7"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A48" s="79"/>
+      <c r="A48" s="54"/>
       <c r="B48" s="38"/>
       <c r="C48" s="34"/>
       <c r="D48" s="34"/>
@@ -1954,7 +2008,7 @@
       <c r="I48" s="7"/>
     </row>
     <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="79"/>
+      <c r="A49" s="54"/>
       <c r="B49" s="38"/>
       <c r="C49" s="34"/>
       <c r="D49" s="34"/>
@@ -1965,7 +2019,7 @@
       <c r="I49" s="7"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A50" s="79"/>
+      <c r="A50" s="54"/>
       <c r="B50" s="38"/>
       <c r="C50" s="34"/>
       <c r="D50" s="34"/>
@@ -1976,7 +2030,7 @@
       <c r="I50" s="7"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A51" s="79"/>
+      <c r="A51" s="54"/>
       <c r="B51" s="38"/>
       <c r="C51" s="34"/>
       <c r="D51" s="34"/>
@@ -1987,7 +2041,7 @@
       <c r="I51" s="7"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A52" s="79"/>
+      <c r="A52" s="54"/>
       <c r="B52" s="33"/>
       <c r="C52" s="34"/>
       <c r="D52" s="34"/>
@@ -1998,7 +2052,7 @@
       <c r="I52" s="7"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A53" s="79"/>
+      <c r="A53" s="54"/>
       <c r="B53" s="33"/>
       <c r="C53" s="34"/>
       <c r="D53" s="34"/>
@@ -2009,7 +2063,7 @@
       <c r="I53" s="7"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A54" s="79"/>
+      <c r="A54" s="54"/>
       <c r="B54" s="33"/>
       <c r="C54" s="34"/>
       <c r="D54" s="34"/>
@@ -2020,7 +2074,7 @@
       <c r="I54" s="7"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A55" s="79"/>
+      <c r="A55" s="54"/>
       <c r="B55" s="33"/>
       <c r="C55" s="34"/>
       <c r="D55" s="34"/>
@@ -2031,7 +2085,7 @@
       <c r="I55" s="7"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A56" s="79"/>
+      <c r="A56" s="54"/>
       <c r="B56" s="33"/>
       <c r="C56" s="34"/>
       <c r="D56" s="34"/>
@@ -2042,7 +2096,7 @@
       <c r="I56" s="7"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A57" s="79"/>
+      <c r="A57" s="54"/>
       <c r="B57" s="33"/>
       <c r="C57" s="34"/>
       <c r="D57" s="34"/>
@@ -2053,7 +2107,7 @@
       <c r="I57" s="7"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A58" s="79"/>
+      <c r="A58" s="54"/>
       <c r="B58" s="33"/>
       <c r="C58" s="34"/>
       <c r="D58" s="34"/>
@@ -2064,7 +2118,7 @@
       <c r="I58" s="7"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A59" s="79"/>
+      <c r="A59" s="54"/>
       <c r="B59" s="33"/>
       <c r="C59" s="34"/>
       <c r="D59" s="34"/>
@@ -2075,7 +2129,7 @@
       <c r="I59" s="7"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A60" s="79"/>
+      <c r="A60" s="54"/>
       <c r="B60" s="33"/>
       <c r="C60" s="34"/>
       <c r="D60" s="34"/>
@@ -2086,7 +2140,7 @@
       <c r="I60" s="7"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A61" s="79"/>
+      <c r="A61" s="54"/>
       <c r="B61" s="33"/>
       <c r="C61" s="34"/>
       <c r="D61" s="34"/>
@@ -2097,7 +2151,7 @@
       <c r="I61" s="7"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A62" s="79"/>
+      <c r="A62" s="54"/>
       <c r="B62" s="33"/>
       <c r="C62" s="34"/>
       <c r="D62" s="34"/>
@@ -2108,7 +2162,7 @@
       <c r="I62" s="7"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A63" s="79"/>
+      <c r="A63" s="54"/>
       <c r="B63" s="33"/>
       <c r="C63" s="34"/>
       <c r="D63" s="34"/>
@@ -2119,10 +2173,10 @@
       <c r="I63" s="7"/>
     </row>
     <row r="64" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="80"/>
-      <c r="B64" s="49"/>
-      <c r="C64" s="50"/>
-      <c r="D64" s="50"/>
+      <c r="A64" s="55"/>
+      <c r="B64" s="64"/>
+      <c r="C64" s="76"/>
+      <c r="D64" s="76"/>
       <c r="E64" s="22"/>
       <c r="F64" s="23"/>
       <c r="G64" s="23"/>
@@ -2130,14 +2184,14 @@
       <c r="I64" s="25"/>
     </row>
     <row r="65" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="75" t="s">
+      <c r="A65" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="B65" s="76"/>
-      <c r="C65" s="76"/>
-      <c r="D65" s="76"/>
-      <c r="E65" s="76"/>
-      <c r="F65" s="77"/>
+      <c r="B65" s="51"/>
+      <c r="C65" s="51"/>
+      <c r="D65" s="51"/>
+      <c r="E65" s="51"/>
+      <c r="F65" s="52"/>
       <c r="G65" s="27">
         <f>I65/1.1</f>
         <v>0</v>
@@ -2152,10 +2206,10 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="51"/>
-      <c r="B66" s="52"/>
-      <c r="C66" s="52"/>
-      <c r="D66" s="52"/>
+      <c r="A66" s="77"/>
+      <c r="B66" s="37"/>
+      <c r="C66" s="37"/>
+      <c r="D66" s="37"/>
       <c r="E66" s="18"/>
       <c r="F66" s="18"/>
       <c r="G66" s="19"/>
@@ -2163,88 +2217,120 @@
       <c r="I66" s="20"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A67" s="67" t="s">
+      <c r="A67" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B67" s="68"/>
-      <c r="C67" s="68"/>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
-      <c r="H67" s="68"/>
-      <c r="I67" s="69"/>
+      <c r="B67" s="40"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="40"/>
+      <c r="E67" s="40"/>
+      <c r="F67" s="40"/>
+      <c r="G67" s="40"/>
+      <c r="H67" s="40"/>
+      <c r="I67" s="41"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A68" s="40" t="s">
+      <c r="A68" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
-      <c r="F68" s="36"/>
-      <c r="G68" s="36"/>
-      <c r="H68" s="36"/>
-      <c r="I68" s="37"/>
+      <c r="B68" s="58"/>
+      <c r="C68" s="58"/>
+      <c r="D68" s="58"/>
+      <c r="E68" s="58"/>
+      <c r="F68" s="58"/>
+      <c r="G68" s="58"/>
+      <c r="H68" s="58"/>
+      <c r="I68" s="59"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A69" s="40" t="s">
+      <c r="A69" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="B69" s="36"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="36"/>
-      <c r="H69" s="36"/>
-      <c r="I69" s="37"/>
+      <c r="B69" s="58"/>
+      <c r="C69" s="58"/>
+      <c r="D69" s="58"/>
+      <c r="E69" s="58"/>
+      <c r="F69" s="58"/>
+      <c r="G69" s="58"/>
+      <c r="H69" s="58"/>
+      <c r="I69" s="59"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A70" s="40" t="s">
+      <c r="A70" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="36"/>
-      <c r="I70" s="37"/>
+      <c r="B70" s="58"/>
+      <c r="C70" s="58"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="58"/>
+      <c r="F70" s="58"/>
+      <c r="G70" s="58"/>
+      <c r="H70" s="58"/>
+      <c r="I70" s="59"/>
     </row>
     <row r="71" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="59" t="s">
+      <c r="A71" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="B71" s="60"/>
-      <c r="C71" s="60"/>
-      <c r="D71" s="60"/>
-      <c r="E71" s="60"/>
-      <c r="F71" s="60"/>
-      <c r="G71" s="60"/>
-      <c r="H71" s="60"/>
-      <c r="I71" s="61"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="45"/>
+      <c r="D71" s="45"/>
+      <c r="E71" s="45"/>
+      <c r="F71" s="45"/>
+      <c r="G71" s="45"/>
+      <c r="H71" s="45"/>
+      <c r="I71" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E4:F5"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B18:D18"/>
@@ -2261,54 +2347,975 @@
     <mergeCell ref="A10:A64"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C전체 &amp;N 페이지 중 &amp;P 페이지</oddFooter>
+    <evenFooter>&amp;C전체 &amp;N 페이지 중 &amp;P 페이지</evenFooter>
+    <firstFooter>&amp;C전체 &amp;N 페이지 중 &amp;P 페이지</firstFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D73A784-57A4-419A-BE10-1D6AFCF67182}">
+  <dimension ref="A1:I71"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="3.59765625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="8.3984375" customWidth="1"/>
+    <col min="3" max="3" width="29.19921875" style="13" customWidth="1"/>
+    <col min="4" max="4" width="3.3984375" style="13" customWidth="1"/>
+    <col min="5" max="5" width="4.796875" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.8984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.8984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="13" customWidth="1"/>
+    <col min="9" max="9" width="10.8984375" style="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+    </row>
+    <row r="2" spans="1:9" ht="6.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="49"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+    </row>
+    <row r="3" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="72">
+        <f ca="1">TODAY()</f>
+        <v>46110</v>
+      </c>
+      <c r="B3" s="73"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="48"/>
+      <c r="G3" s="74" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="73"/>
+      <c r="I3" s="75"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A4" s="26"/>
+      <c r="C4" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="70"/>
+      <c r="E4" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="60"/>
+      <c r="G4" s="66" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="58"/>
+      <c r="I4" s="59"/>
+    </row>
+    <row r="5" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="14"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="58"/>
+      <c r="I5" s="59"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6" s="14"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="56"/>
+      <c r="G6" s="66" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="58"/>
+      <c r="I6" s="59"/>
+    </row>
+    <row r="7" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="65"/>
+      <c r="G7" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="45"/>
+      <c r="I7" s="46"/>
+    </row>
+    <row r="8" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="43"/>
+    </row>
+    <row r="9" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="73"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="78"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="31"/>
+    </row>
+    <row r="11" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="54"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="54"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="54"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="54"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A15" s="54"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16" s="54"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="54"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A18" s="54"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19" s="54"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="54"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A21" s="54"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22" s="54"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="54"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" s="54"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25" s="54"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" s="54"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="7"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27" s="54"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="7"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28" s="54"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A29" s="54"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="7"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A30" s="54"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="7"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A31" s="54"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A32" s="54"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="7"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A33" s="54"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="7"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A34" s="54"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="7"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A35" s="54"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A36" s="54"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="7"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A37" s="54"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A38" s="54"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="7"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A39" s="54"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A40" s="54"/>
+      <c r="B40" s="33"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="7"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A41" s="54"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="7"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A42" s="54"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A43" s="54"/>
+      <c r="B43" s="33"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A44" s="54"/>
+      <c r="B44" s="33"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="7"/>
+    </row>
+    <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="54"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A46" s="54"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A47" s="54"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="7"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A48" s="54"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="7"/>
+    </row>
+    <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="54"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="7"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A50" s="54"/>
+      <c r="B50" s="38"/>
+      <c r="C50" s="34"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="7"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A51" s="54"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="7"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A52" s="54"/>
+      <c r="B52" s="33"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="7"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A53" s="54"/>
+      <c r="B53" s="33"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="7"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A54" s="54"/>
+      <c r="B54" s="33"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="7"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A55" s="54"/>
+      <c r="B55" s="33"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A56" s="54"/>
+      <c r="B56" s="33"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="7"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A57" s="54"/>
+      <c r="B57" s="33"/>
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A58" s="54"/>
+      <c r="B58" s="33"/>
+      <c r="C58" s="34"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="7"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A59" s="54"/>
+      <c r="B59" s="33"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="7"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A60" s="54"/>
+      <c r="B60" s="33"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="7"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A61" s="54"/>
+      <c r="B61" s="33"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A62" s="54"/>
+      <c r="B62" s="33"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="7"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A63" s="54"/>
+      <c r="B63" s="33"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="7"/>
+    </row>
+    <row r="64" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="55"/>
+      <c r="B64" s="64"/>
+      <c r="C64" s="76"/>
+      <c r="D64" s="76"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="23"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="24"/>
+      <c r="I64" s="25"/>
+    </row>
+    <row r="65" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65" s="51"/>
+      <c r="C65" s="51"/>
+      <c r="D65" s="51"/>
+      <c r="E65" s="51"/>
+      <c r="F65" s="52"/>
+      <c r="G65" s="27">
+        <f>I65/1.1</f>
+        <v>0</v>
+      </c>
+      <c r="H65" s="28">
+        <f t="shared" ref="H65" si="0">G65*0.1</f>
+        <v>0</v>
+      </c>
+      <c r="I65" s="29">
+        <f>SUM(I10:I64)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="77"/>
+      <c r="B66" s="37"/>
+      <c r="C66" s="37"/>
+      <c r="D66" s="37"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="20"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A67" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="40"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="40"/>
+      <c r="E67" s="40"/>
+      <c r="F67" s="40"/>
+      <c r="G67" s="40"/>
+      <c r="H67" s="40"/>
+      <c r="I67" s="41"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A68" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="B68" s="58"/>
+      <c r="C68" s="58"/>
+      <c r="D68" s="58"/>
+      <c r="E68" s="58"/>
+      <c r="F68" s="58"/>
+      <c r="G68" s="58"/>
+      <c r="H68" s="58"/>
+      <c r="I68" s="59"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A69" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" s="58"/>
+      <c r="C69" s="58"/>
+      <c r="D69" s="58"/>
+      <c r="E69" s="58"/>
+      <c r="F69" s="58"/>
+      <c r="G69" s="58"/>
+      <c r="H69" s="58"/>
+      <c r="I69" s="59"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A70" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" s="58"/>
+      <c r="C70" s="58"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="58"/>
+      <c r="F70" s="58"/>
+      <c r="G70" s="58"/>
+      <c r="H70" s="58"/>
+      <c r="I70" s="59"/>
+    </row>
+    <row r="71" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="B71" s="45"/>
+      <c r="C71" s="45"/>
+      <c r="D71" s="45"/>
+      <c r="E71" s="45"/>
+      <c r="F71" s="45"/>
+      <c r="G71" s="45"/>
+      <c r="H71" s="45"/>
+      <c r="I71" s="46"/>
+    </row>
+  </sheetData>
+  <mergeCells count="80">
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A69:I69"/>
     <mergeCell ref="A70:I70"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E4:F5"/>
     <mergeCell ref="A71:I71"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B48:D48"/>
     <mergeCell ref="B49:D49"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:A64"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="E4:F5"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="G5:I5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/견적서_template.xlsx
+++ b/templates/견적서_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DAILYCIGAR_DB\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96847785-3CDA-4C97-A7EF-94FB127C953A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232D9337-815C-405F-994A-8ACF7D98F02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서_기본" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
   <si>
     <t>견 적 서</t>
   </si>
@@ -51,26 +51,14 @@
     <t>상    호</t>
   </si>
   <si>
-    <t xml:space="preserve">롤로만수점 </t>
-  </si>
-  <si>
     <t>사업장 
 주소</t>
-  </si>
-  <si>
-    <t>인천 남동구 하촌로 7 101호</t>
   </si>
   <si>
     <t>담 당 자</t>
   </si>
   <si>
-    <t>롤로만수점 대표님</t>
-  </si>
-  <si>
     <t>TEL</t>
-  </si>
-  <si>
-    <t>010-2370-1452</t>
   </si>
   <si>
     <t xml:space="preserve"> 금 액 (견적금액) : 1,715,000 원 (V.A.T. 제외)</t>
@@ -934,97 +922,97 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="13" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="31" fontId="11" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="13" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="31" fontId="11" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="17">
     <cellStyle name="쉼표 [0]" xfId="13" builtinId="6"/>
@@ -1440,149 +1428,139 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
     </row>
     <row r="2" spans="1:9" ht="6.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="49"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="72">
+      <c r="A3" s="44">
         <f ca="1">TODAY()</f>
-        <v>46110</v>
-      </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="69" t="s">
+        <v>46111</v>
+      </c>
+      <c r="B3" s="45"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="47" t="s">
+      <c r="E3" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="48"/>
-      <c r="G3" s="74" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="73"/>
-      <c r="I3" s="75"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="48"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="26"/>
-      <c r="C4" s="81" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="70"/>
+      <c r="C4" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="42"/>
       <c r="E4" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="60"/>
-      <c r="G4" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="58"/>
-      <c r="I4" s="59"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="37"/>
     </row>
     <row r="5" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="66" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="58"/>
-      <c r="I5" s="59"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="37"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="14"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="70"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="56"/>
-      <c r="G6" s="66" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="58"/>
-      <c r="I6" s="59"/>
+        <v>4</v>
+      </c>
+      <c r="F6" s="81"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="37"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="15"/>
       <c r="B7" s="16"/>
       <c r="C7" s="17"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="65"/>
-      <c r="G7" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="45"/>
-      <c r="I7" s="46"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="62"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="61"/>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
+      <c r="A8" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
       <c r="D8" s="32"/>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="43"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="71"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="21" t="s">
+      <c r="I9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="21" t="s">
+    </row>
+    <row r="10" spans="1:9" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="78"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
       <c r="E10" s="30"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -1590,7 +1568,7 @@
       <c r="I10" s="31"/>
     </row>
     <row r="11" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="54"/>
+      <c r="A11" s="79"/>
       <c r="B11" s="33"/>
       <c r="C11" s="34"/>
       <c r="D11" s="34"/>
@@ -1601,7 +1579,7 @@
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="54"/>
+      <c r="A12" s="79"/>
       <c r="B12" s="33"/>
       <c r="C12" s="34"/>
       <c r="D12" s="34"/>
@@ -1612,7 +1590,7 @@
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="54"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="33"/>
       <c r="C13" s="34"/>
       <c r="D13" s="34"/>
@@ -1623,7 +1601,7 @@
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="54"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="33"/>
       <c r="C14" s="34"/>
       <c r="D14" s="34"/>
@@ -1634,7 +1612,7 @@
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="54"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="38"/>
       <c r="C15" s="34"/>
       <c r="D15" s="34"/>
@@ -1645,7 +1623,7 @@
       <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="54"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="38"/>
       <c r="C16" s="34"/>
       <c r="D16" s="34"/>
@@ -1656,7 +1634,7 @@
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="54"/>
+      <c r="A17" s="79"/>
       <c r="B17" s="38"/>
       <c r="C17" s="34"/>
       <c r="D17" s="34"/>
@@ -1667,7 +1645,7 @@
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="54"/>
+      <c r="A18" s="79"/>
       <c r="B18" s="38"/>
       <c r="C18" s="34"/>
       <c r="D18" s="34"/>
@@ -1678,7 +1656,7 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="54"/>
+      <c r="A19" s="79"/>
       <c r="B19" s="38"/>
       <c r="C19" s="34"/>
       <c r="D19" s="34"/>
@@ -1689,7 +1667,7 @@
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="54"/>
+      <c r="A20" s="79"/>
       <c r="B20" s="38"/>
       <c r="C20" s="34"/>
       <c r="D20" s="34"/>
@@ -1700,7 +1678,7 @@
       <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="54"/>
+      <c r="A21" s="79"/>
       <c r="B21" s="38"/>
       <c r="C21" s="34"/>
       <c r="D21" s="34"/>
@@ -1711,7 +1689,7 @@
       <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="54"/>
+      <c r="A22" s="79"/>
       <c r="B22" s="38"/>
       <c r="C22" s="34"/>
       <c r="D22" s="34"/>
@@ -1722,7 +1700,7 @@
       <c r="I22" s="7"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="54"/>
+      <c r="A23" s="79"/>
       <c r="B23" s="38"/>
       <c r="C23" s="34"/>
       <c r="D23" s="34"/>
@@ -1733,7 +1711,7 @@
       <c r="I23" s="7"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="54"/>
+      <c r="A24" s="79"/>
       <c r="B24" s="38"/>
       <c r="C24" s="34"/>
       <c r="D24" s="34"/>
@@ -1744,7 +1722,7 @@
       <c r="I24" s="7"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="54"/>
+      <c r="A25" s="79"/>
       <c r="B25" s="38"/>
       <c r="C25" s="34"/>
       <c r="D25" s="34"/>
@@ -1755,7 +1733,7 @@
       <c r="I25" s="7"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="54"/>
+      <c r="A26" s="79"/>
       <c r="B26" s="38"/>
       <c r="C26" s="34"/>
       <c r="D26" s="34"/>
@@ -1766,7 +1744,7 @@
       <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="54"/>
+      <c r="A27" s="79"/>
       <c r="B27" s="33"/>
       <c r="C27" s="34"/>
       <c r="D27" s="34"/>
@@ -1777,7 +1755,7 @@
       <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="54"/>
+      <c r="A28" s="79"/>
       <c r="B28" s="33"/>
       <c r="C28" s="34"/>
       <c r="D28" s="34"/>
@@ -1788,7 +1766,7 @@
       <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="54"/>
+      <c r="A29" s="79"/>
       <c r="B29" s="33"/>
       <c r="C29" s="34"/>
       <c r="D29" s="34"/>
@@ -1799,7 +1777,7 @@
       <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="54"/>
+      <c r="A30" s="79"/>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
       <c r="D30" s="34"/>
@@ -1810,7 +1788,7 @@
       <c r="I30" s="7"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="54"/>
+      <c r="A31" s="79"/>
       <c r="B31" s="33"/>
       <c r="C31" s="34"/>
       <c r="D31" s="34"/>
@@ -1821,7 +1799,7 @@
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="54"/>
+      <c r="A32" s="79"/>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
       <c r="D32" s="34"/>
@@ -1832,7 +1810,7 @@
       <c r="I32" s="7"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A33" s="54"/>
+      <c r="A33" s="79"/>
       <c r="B33" s="33"/>
       <c r="C33" s="34"/>
       <c r="D33" s="34"/>
@@ -1843,7 +1821,7 @@
       <c r="I33" s="7"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="54"/>
+      <c r="A34" s="79"/>
       <c r="B34" s="33"/>
       <c r="C34" s="34"/>
       <c r="D34" s="34"/>
@@ -1854,7 +1832,7 @@
       <c r="I34" s="7"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A35" s="54"/>
+      <c r="A35" s="79"/>
       <c r="B35" s="33"/>
       <c r="C35" s="34"/>
       <c r="D35" s="34"/>
@@ -1865,7 +1843,7 @@
       <c r="I35" s="7"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A36" s="54"/>
+      <c r="A36" s="79"/>
       <c r="B36" s="33"/>
       <c r="C36" s="34"/>
       <c r="D36" s="34"/>
@@ -1876,7 +1854,7 @@
       <c r="I36" s="7"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A37" s="54"/>
+      <c r="A37" s="79"/>
       <c r="B37" s="33"/>
       <c r="C37" s="34"/>
       <c r="D37" s="34"/>
@@ -1887,7 +1865,7 @@
       <c r="I37" s="7"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="54"/>
+      <c r="A38" s="79"/>
       <c r="B38" s="33"/>
       <c r="C38" s="34"/>
       <c r="D38" s="34"/>
@@ -1898,7 +1876,7 @@
       <c r="I38" s="7"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="54"/>
+      <c r="A39" s="79"/>
       <c r="B39" s="33"/>
       <c r="C39" s="34"/>
       <c r="D39" s="34"/>
@@ -1909,7 +1887,7 @@
       <c r="I39" s="7"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A40" s="54"/>
+      <c r="A40" s="79"/>
       <c r="B40" s="33"/>
       <c r="C40" s="34"/>
       <c r="D40" s="34"/>
@@ -1920,7 +1898,7 @@
       <c r="I40" s="7"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A41" s="54"/>
+      <c r="A41" s="79"/>
       <c r="B41" s="33"/>
       <c r="C41" s="34"/>
       <c r="D41" s="34"/>
@@ -1931,7 +1909,7 @@
       <c r="I41" s="7"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A42" s="54"/>
+      <c r="A42" s="79"/>
       <c r="B42" s="33"/>
       <c r="C42" s="34"/>
       <c r="D42" s="34"/>
@@ -1942,7 +1920,7 @@
       <c r="I42" s="7"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A43" s="54"/>
+      <c r="A43" s="79"/>
       <c r="B43" s="33"/>
       <c r="C43" s="34"/>
       <c r="D43" s="34"/>
@@ -1953,7 +1931,7 @@
       <c r="I43" s="7"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A44" s="54"/>
+      <c r="A44" s="79"/>
       <c r="B44" s="33"/>
       <c r="C44" s="34"/>
       <c r="D44" s="34"/>
@@ -1964,7 +1942,7 @@
       <c r="I44" s="7"/>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="54"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="38"/>
       <c r="C45" s="34"/>
       <c r="D45" s="34"/>
@@ -1975,7 +1953,7 @@
       <c r="I45" s="7"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A46" s="54"/>
+      <c r="A46" s="79"/>
       <c r="B46" s="38"/>
       <c r="C46" s="34"/>
       <c r="D46" s="34"/>
@@ -1986,7 +1964,7 @@
       <c r="I46" s="7"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A47" s="54"/>
+      <c r="A47" s="79"/>
       <c r="B47" s="38"/>
       <c r="C47" s="34"/>
       <c r="D47" s="34"/>
@@ -1997,7 +1975,7 @@
       <c r="I47" s="7"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A48" s="54"/>
+      <c r="A48" s="79"/>
       <c r="B48" s="38"/>
       <c r="C48" s="34"/>
       <c r="D48" s="34"/>
@@ -2008,7 +1986,7 @@
       <c r="I48" s="7"/>
     </row>
     <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="54"/>
+      <c r="A49" s="79"/>
       <c r="B49" s="38"/>
       <c r="C49" s="34"/>
       <c r="D49" s="34"/>
@@ -2019,7 +1997,7 @@
       <c r="I49" s="7"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A50" s="54"/>
+      <c r="A50" s="79"/>
       <c r="B50" s="38"/>
       <c r="C50" s="34"/>
       <c r="D50" s="34"/>
@@ -2030,7 +2008,7 @@
       <c r="I50" s="7"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A51" s="54"/>
+      <c r="A51" s="79"/>
       <c r="B51" s="38"/>
       <c r="C51" s="34"/>
       <c r="D51" s="34"/>
@@ -2041,7 +2019,7 @@
       <c r="I51" s="7"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A52" s="54"/>
+      <c r="A52" s="79"/>
       <c r="B52" s="33"/>
       <c r="C52" s="34"/>
       <c r="D52" s="34"/>
@@ -2052,7 +2030,7 @@
       <c r="I52" s="7"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A53" s="54"/>
+      <c r="A53" s="79"/>
       <c r="B53" s="33"/>
       <c r="C53" s="34"/>
       <c r="D53" s="34"/>
@@ -2063,7 +2041,7 @@
       <c r="I53" s="7"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A54" s="54"/>
+      <c r="A54" s="79"/>
       <c r="B54" s="33"/>
       <c r="C54" s="34"/>
       <c r="D54" s="34"/>
@@ -2074,7 +2052,7 @@
       <c r="I54" s="7"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A55" s="54"/>
+      <c r="A55" s="79"/>
       <c r="B55" s="33"/>
       <c r="C55" s="34"/>
       <c r="D55" s="34"/>
@@ -2085,7 +2063,7 @@
       <c r="I55" s="7"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A56" s="54"/>
+      <c r="A56" s="79"/>
       <c r="B56" s="33"/>
       <c r="C56" s="34"/>
       <c r="D56" s="34"/>
@@ -2096,7 +2074,7 @@
       <c r="I56" s="7"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A57" s="54"/>
+      <c r="A57" s="79"/>
       <c r="B57" s="33"/>
       <c r="C57" s="34"/>
       <c r="D57" s="34"/>
@@ -2107,7 +2085,7 @@
       <c r="I57" s="7"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A58" s="54"/>
+      <c r="A58" s="79"/>
       <c r="B58" s="33"/>
       <c r="C58" s="34"/>
       <c r="D58" s="34"/>
@@ -2118,7 +2096,7 @@
       <c r="I58" s="7"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A59" s="54"/>
+      <c r="A59" s="79"/>
       <c r="B59" s="33"/>
       <c r="C59" s="34"/>
       <c r="D59" s="34"/>
@@ -2129,7 +2107,7 @@
       <c r="I59" s="7"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A60" s="54"/>
+      <c r="A60" s="79"/>
       <c r="B60" s="33"/>
       <c r="C60" s="34"/>
       <c r="D60" s="34"/>
@@ -2140,7 +2118,7 @@
       <c r="I60" s="7"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A61" s="54"/>
+      <c r="A61" s="79"/>
       <c r="B61" s="33"/>
       <c r="C61" s="34"/>
       <c r="D61" s="34"/>
@@ -2151,7 +2129,7 @@
       <c r="I61" s="7"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A62" s="54"/>
+      <c r="A62" s="79"/>
       <c r="B62" s="33"/>
       <c r="C62" s="34"/>
       <c r="D62" s="34"/>
@@ -2162,7 +2140,7 @@
       <c r="I62" s="7"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A63" s="54"/>
+      <c r="A63" s="79"/>
       <c r="B63" s="33"/>
       <c r="C63" s="34"/>
       <c r="D63" s="34"/>
@@ -2173,10 +2151,10 @@
       <c r="I63" s="7"/>
     </row>
     <row r="64" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="55"/>
-      <c r="B64" s="64"/>
-      <c r="C64" s="76"/>
-      <c r="D64" s="76"/>
+      <c r="A64" s="80"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="50"/>
+      <c r="D64" s="50"/>
       <c r="E64" s="22"/>
       <c r="F64" s="23"/>
       <c r="G64" s="23"/>
@@ -2184,14 +2162,14 @@
       <c r="I64" s="25"/>
     </row>
     <row r="65" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="B65" s="51"/>
-      <c r="C65" s="51"/>
-      <c r="D65" s="51"/>
-      <c r="E65" s="51"/>
-      <c r="F65" s="52"/>
+      <c r="A65" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="B65" s="76"/>
+      <c r="C65" s="76"/>
+      <c r="D65" s="76"/>
+      <c r="E65" s="76"/>
+      <c r="F65" s="77"/>
       <c r="G65" s="27">
         <f>I65/1.1</f>
         <v>0</v>
@@ -2206,10 +2184,10 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="77"/>
-      <c r="B66" s="37"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
+      <c r="A66" s="51"/>
+      <c r="B66" s="52"/>
+      <c r="C66" s="52"/>
+      <c r="D66" s="52"/>
       <c r="E66" s="18"/>
       <c r="F66" s="18"/>
       <c r="G66" s="19"/>
@@ -2217,72 +2195,136 @@
       <c r="I66" s="20"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A67" s="39" t="s">
+      <c r="A67" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" s="68"/>
+      <c r="C67" s="68"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="68"/>
+      <c r="F67" s="68"/>
+      <c r="G67" s="68"/>
+      <c r="H67" s="68"/>
+      <c r="I67" s="69"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A68" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="36"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="36"/>
+      <c r="G68" s="36"/>
+      <c r="H68" s="36"/>
+      <c r="I68" s="37"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A69" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="B69" s="36"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="36"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="36"/>
+      <c r="G69" s="36"/>
+      <c r="H69" s="36"/>
+      <c r="I69" s="37"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A70" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="36"/>
+      <c r="G70" s="36"/>
+      <c r="H70" s="36"/>
+      <c r="I70" s="37"/>
+    </row>
+    <row r="71" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B67" s="40"/>
-      <c r="C67" s="40"/>
-      <c r="D67" s="40"/>
-      <c r="E67" s="40"/>
-      <c r="F67" s="40"/>
-      <c r="G67" s="40"/>
-      <c r="H67" s="40"/>
-      <c r="I67" s="41"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A68" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="B68" s="58"/>
-      <c r="C68" s="58"/>
-      <c r="D68" s="58"/>
-      <c r="E68" s="58"/>
-      <c r="F68" s="58"/>
-      <c r="G68" s="58"/>
-      <c r="H68" s="58"/>
-      <c r="I68" s="59"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A69" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="B69" s="58"/>
-      <c r="C69" s="58"/>
-      <c r="D69" s="58"/>
-      <c r="E69" s="58"/>
-      <c r="F69" s="58"/>
-      <c r="G69" s="58"/>
-      <c r="H69" s="58"/>
-      <c r="I69" s="59"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A70" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="B70" s="58"/>
-      <c r="C70" s="58"/>
-      <c r="D70" s="58"/>
-      <c r="E70" s="58"/>
-      <c r="F70" s="58"/>
-      <c r="G70" s="58"/>
-      <c r="H70" s="58"/>
-      <c r="I70" s="59"/>
-    </row>
-    <row r="71" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="63" t="s">
-        <v>23</v>
-      </c>
-      <c r="B71" s="45"/>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="45"/>
-      <c r="H71" s="45"/>
-      <c r="I71" s="46"/>
+      <c r="B71" s="60"/>
+      <c r="C71" s="60"/>
+      <c r="D71" s="60"/>
+      <c r="E71" s="60"/>
+      <c r="F71" s="60"/>
+      <c r="G71" s="60"/>
+      <c r="H71" s="60"/>
+      <c r="I71" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="A10:A64"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E4:F5"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="G6:I6"/>
@@ -2299,70 +2341,6 @@
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E4:F5"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="A67:I67"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="A10:A64"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2393,149 +2371,139 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
     </row>
     <row r="2" spans="1:9" ht="6.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="49"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="72">
+      <c r="A3" s="44">
         <f ca="1">TODAY()</f>
-        <v>46110</v>
-      </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="69" t="s">
+        <v>46111</v>
+      </c>
+      <c r="B3" s="45"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="47" t="s">
+      <c r="E3" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="48"/>
-      <c r="G3" s="74" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="73"/>
-      <c r="I3" s="75"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="48"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="26"/>
-      <c r="C4" s="81" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="70"/>
+      <c r="C4" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="42"/>
       <c r="E4" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="60"/>
-      <c r="G4" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="58"/>
-      <c r="I4" s="59"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="37"/>
     </row>
     <row r="5" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="66" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="58"/>
-      <c r="I5" s="59"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="37"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="14"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="70"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="56"/>
-      <c r="G6" s="66" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="58"/>
-      <c r="I6" s="59"/>
+        <v>4</v>
+      </c>
+      <c r="F6" s="81"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="37"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="15"/>
       <c r="B7" s="16"/>
       <c r="C7" s="17"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="65"/>
-      <c r="G7" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="45"/>
-      <c r="I7" s="46"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="62"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="61"/>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
+      <c r="A8" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
       <c r="D8" s="32"/>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="43"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="71"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="21" t="s">
+      <c r="I9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="21" t="s">
+    </row>
+    <row r="10" spans="1:9" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="78"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
       <c r="E10" s="30"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
@@ -2543,7 +2511,7 @@
       <c r="I10" s="31"/>
     </row>
     <row r="11" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="54"/>
+      <c r="A11" s="79"/>
       <c r="B11" s="33"/>
       <c r="C11" s="34"/>
       <c r="D11" s="34"/>
@@ -2554,7 +2522,7 @@
       <c r="I11" s="7"/>
     </row>
     <row r="12" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="54"/>
+      <c r="A12" s="79"/>
       <c r="B12" s="33"/>
       <c r="C12" s="34"/>
       <c r="D12" s="34"/>
@@ -2565,7 +2533,7 @@
       <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="54"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="33"/>
       <c r="C13" s="34"/>
       <c r="D13" s="34"/>
@@ -2576,7 +2544,7 @@
       <c r="I13" s="7"/>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="54"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="33"/>
       <c r="C14" s="34"/>
       <c r="D14" s="34"/>
@@ -2587,7 +2555,7 @@
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="54"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="38"/>
       <c r="C15" s="34"/>
       <c r="D15" s="34"/>
@@ -2598,7 +2566,7 @@
       <c r="I15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="54"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="38"/>
       <c r="C16" s="34"/>
       <c r="D16" s="34"/>
@@ -2609,7 +2577,7 @@
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="54"/>
+      <c r="A17" s="79"/>
       <c r="B17" s="38"/>
       <c r="C17" s="34"/>
       <c r="D17" s="34"/>
@@ -2620,7 +2588,7 @@
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="54"/>
+      <c r="A18" s="79"/>
       <c r="B18" s="38"/>
       <c r="C18" s="34"/>
       <c r="D18" s="34"/>
@@ -2631,7 +2599,7 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="54"/>
+      <c r="A19" s="79"/>
       <c r="B19" s="38"/>
       <c r="C19" s="34"/>
       <c r="D19" s="34"/>
@@ -2642,7 +2610,7 @@
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="54"/>
+      <c r="A20" s="79"/>
       <c r="B20" s="38"/>
       <c r="C20" s="34"/>
       <c r="D20" s="34"/>
@@ -2653,7 +2621,7 @@
       <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="54"/>
+      <c r="A21" s="79"/>
       <c r="B21" s="38"/>
       <c r="C21" s="34"/>
       <c r="D21" s="34"/>
@@ -2664,7 +2632,7 @@
       <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="54"/>
+      <c r="A22" s="79"/>
       <c r="B22" s="38"/>
       <c r="C22" s="34"/>
       <c r="D22" s="34"/>
@@ -2675,7 +2643,7 @@
       <c r="I22" s="7"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="54"/>
+      <c r="A23" s="79"/>
       <c r="B23" s="38"/>
       <c r="C23" s="34"/>
       <c r="D23" s="34"/>
@@ -2686,7 +2654,7 @@
       <c r="I23" s="7"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="54"/>
+      <c r="A24" s="79"/>
       <c r="B24" s="38"/>
       <c r="C24" s="34"/>
       <c r="D24" s="34"/>
@@ -2697,7 +2665,7 @@
       <c r="I24" s="7"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="54"/>
+      <c r="A25" s="79"/>
       <c r="B25" s="38"/>
       <c r="C25" s="34"/>
       <c r="D25" s="34"/>
@@ -2708,7 +2676,7 @@
       <c r="I25" s="7"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="54"/>
+      <c r="A26" s="79"/>
       <c r="B26" s="38"/>
       <c r="C26" s="34"/>
       <c r="D26" s="34"/>
@@ -2719,7 +2687,7 @@
       <c r="I26" s="7"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="54"/>
+      <c r="A27" s="79"/>
       <c r="B27" s="33"/>
       <c r="C27" s="34"/>
       <c r="D27" s="34"/>
@@ -2730,7 +2698,7 @@
       <c r="I27" s="7"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="54"/>
+      <c r="A28" s="79"/>
       <c r="B28" s="33"/>
       <c r="C28" s="34"/>
       <c r="D28" s="34"/>
@@ -2741,7 +2709,7 @@
       <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="54"/>
+      <c r="A29" s="79"/>
       <c r="B29" s="33"/>
       <c r="C29" s="34"/>
       <c r="D29" s="34"/>
@@ -2752,7 +2720,7 @@
       <c r="I29" s="7"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="54"/>
+      <c r="A30" s="79"/>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
       <c r="D30" s="34"/>
@@ -2763,7 +2731,7 @@
       <c r="I30" s="7"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="54"/>
+      <c r="A31" s="79"/>
       <c r="B31" s="33"/>
       <c r="C31" s="34"/>
       <c r="D31" s="34"/>
@@ -2774,7 +2742,7 @@
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="54"/>
+      <c r="A32" s="79"/>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
       <c r="D32" s="34"/>
@@ -2785,7 +2753,7 @@
       <c r="I32" s="7"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A33" s="54"/>
+      <c r="A33" s="79"/>
       <c r="B33" s="33"/>
       <c r="C33" s="34"/>
       <c r="D33" s="34"/>
@@ -2796,7 +2764,7 @@
       <c r="I33" s="7"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="54"/>
+      <c r="A34" s="79"/>
       <c r="B34" s="33"/>
       <c r="C34" s="34"/>
       <c r="D34" s="34"/>
@@ -2807,7 +2775,7 @@
       <c r="I34" s="7"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A35" s="54"/>
+      <c r="A35" s="79"/>
       <c r="B35" s="33"/>
       <c r="C35" s="34"/>
       <c r="D35" s="34"/>
@@ -2818,7 +2786,7 @@
       <c r="I35" s="7"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A36" s="54"/>
+      <c r="A36" s="79"/>
       <c r="B36" s="33"/>
       <c r="C36" s="34"/>
       <c r="D36" s="34"/>
@@ -2829,7 +2797,7 @@
       <c r="I36" s="7"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A37" s="54"/>
+      <c r="A37" s="79"/>
       <c r="B37" s="33"/>
       <c r="C37" s="34"/>
       <c r="D37" s="34"/>
@@ -2840,7 +2808,7 @@
       <c r="I37" s="7"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="54"/>
+      <c r="A38" s="79"/>
       <c r="B38" s="33"/>
       <c r="C38" s="34"/>
       <c r="D38" s="34"/>
@@ -2851,7 +2819,7 @@
       <c r="I38" s="7"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="54"/>
+      <c r="A39" s="79"/>
       <c r="B39" s="33"/>
       <c r="C39" s="34"/>
       <c r="D39" s="34"/>
@@ -2862,7 +2830,7 @@
       <c r="I39" s="7"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A40" s="54"/>
+      <c r="A40" s="79"/>
       <c r="B40" s="33"/>
       <c r="C40" s="34"/>
       <c r="D40" s="34"/>
@@ -2873,7 +2841,7 @@
       <c r="I40" s="7"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A41" s="54"/>
+      <c r="A41" s="79"/>
       <c r="B41" s="33"/>
       <c r="C41" s="34"/>
       <c r="D41" s="34"/>
@@ -2884,7 +2852,7 @@
       <c r="I41" s="7"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A42" s="54"/>
+      <c r="A42" s="79"/>
       <c r="B42" s="33"/>
       <c r="C42" s="34"/>
       <c r="D42" s="34"/>
@@ -2895,7 +2863,7 @@
       <c r="I42" s="7"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A43" s="54"/>
+      <c r="A43" s="79"/>
       <c r="B43" s="33"/>
       <c r="C43" s="34"/>
       <c r="D43" s="34"/>
@@ -2906,7 +2874,7 @@
       <c r="I43" s="7"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A44" s="54"/>
+      <c r="A44" s="79"/>
       <c r="B44" s="33"/>
       <c r="C44" s="34"/>
       <c r="D44" s="34"/>
@@ -2917,7 +2885,7 @@
       <c r="I44" s="7"/>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="54"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="38"/>
       <c r="C45" s="34"/>
       <c r="D45" s="34"/>
@@ -2928,7 +2896,7 @@
       <c r="I45" s="7"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A46" s="54"/>
+      <c r="A46" s="79"/>
       <c r="B46" s="38"/>
       <c r="C46" s="34"/>
       <c r="D46" s="34"/>
@@ -2939,7 +2907,7 @@
       <c r="I46" s="7"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A47" s="54"/>
+      <c r="A47" s="79"/>
       <c r="B47" s="38"/>
       <c r="C47" s="34"/>
       <c r="D47" s="34"/>
@@ -2950,7 +2918,7 @@
       <c r="I47" s="7"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A48" s="54"/>
+      <c r="A48" s="79"/>
       <c r="B48" s="38"/>
       <c r="C48" s="34"/>
       <c r="D48" s="34"/>
@@ -2961,7 +2929,7 @@
       <c r="I48" s="7"/>
     </row>
     <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="54"/>
+      <c r="A49" s="79"/>
       <c r="B49" s="38"/>
       <c r="C49" s="34"/>
       <c r="D49" s="34"/>
@@ -2972,7 +2940,7 @@
       <c r="I49" s="7"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A50" s="54"/>
+      <c r="A50" s="79"/>
       <c r="B50" s="38"/>
       <c r="C50" s="34"/>
       <c r="D50" s="34"/>
@@ -2983,7 +2951,7 @@
       <c r="I50" s="7"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A51" s="54"/>
+      <c r="A51" s="79"/>
       <c r="B51" s="38"/>
       <c r="C51" s="34"/>
       <c r="D51" s="34"/>
@@ -2994,7 +2962,7 @@
       <c r="I51" s="7"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A52" s="54"/>
+      <c r="A52" s="79"/>
       <c r="B52" s="33"/>
       <c r="C52" s="34"/>
       <c r="D52" s="34"/>
@@ -3005,7 +2973,7 @@
       <c r="I52" s="7"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A53" s="54"/>
+      <c r="A53" s="79"/>
       <c r="B53" s="33"/>
       <c r="C53" s="34"/>
       <c r="D53" s="34"/>
@@ -3016,7 +2984,7 @@
       <c r="I53" s="7"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A54" s="54"/>
+      <c r="A54" s="79"/>
       <c r="B54" s="33"/>
       <c r="C54" s="34"/>
       <c r="D54" s="34"/>
@@ -3027,7 +2995,7 @@
       <c r="I54" s="7"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A55" s="54"/>
+      <c r="A55" s="79"/>
       <c r="B55" s="33"/>
       <c r="C55" s="34"/>
       <c r="D55" s="34"/>
@@ -3038,7 +3006,7 @@
       <c r="I55" s="7"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A56" s="54"/>
+      <c r="A56" s="79"/>
       <c r="B56" s="33"/>
       <c r="C56" s="34"/>
       <c r="D56" s="34"/>
@@ -3049,7 +3017,7 @@
       <c r="I56" s="7"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A57" s="54"/>
+      <c r="A57" s="79"/>
       <c r="B57" s="33"/>
       <c r="C57" s="34"/>
       <c r="D57" s="34"/>
@@ -3060,7 +3028,7 @@
       <c r="I57" s="7"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A58" s="54"/>
+      <c r="A58" s="79"/>
       <c r="B58" s="33"/>
       <c r="C58" s="34"/>
       <c r="D58" s="34"/>
@@ -3071,7 +3039,7 @@
       <c r="I58" s="7"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A59" s="54"/>
+      <c r="A59" s="79"/>
       <c r="B59" s="33"/>
       <c r="C59" s="34"/>
       <c r="D59" s="34"/>
@@ -3082,7 +3050,7 @@
       <c r="I59" s="7"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A60" s="54"/>
+      <c r="A60" s="79"/>
       <c r="B60" s="33"/>
       <c r="C60" s="34"/>
       <c r="D60" s="34"/>
@@ -3093,7 +3061,7 @@
       <c r="I60" s="7"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A61" s="54"/>
+      <c r="A61" s="79"/>
       <c r="B61" s="33"/>
       <c r="C61" s="34"/>
       <c r="D61" s="34"/>
@@ -3104,7 +3072,7 @@
       <c r="I61" s="7"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A62" s="54"/>
+      <c r="A62" s="79"/>
       <c r="B62" s="33"/>
       <c r="C62" s="34"/>
       <c r="D62" s="34"/>
@@ -3115,7 +3083,7 @@
       <c r="I62" s="7"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A63" s="54"/>
+      <c r="A63" s="79"/>
       <c r="B63" s="33"/>
       <c r="C63" s="34"/>
       <c r="D63" s="34"/>
@@ -3126,10 +3094,10 @@
       <c r="I63" s="7"/>
     </row>
     <row r="64" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="55"/>
-      <c r="B64" s="64"/>
-      <c r="C64" s="76"/>
-      <c r="D64" s="76"/>
+      <c r="A64" s="80"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="50"/>
+      <c r="D64" s="50"/>
       <c r="E64" s="22"/>
       <c r="F64" s="23"/>
       <c r="G64" s="23"/>
@@ -3137,14 +3105,14 @@
       <c r="I64" s="25"/>
     </row>
     <row r="65" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="B65" s="51"/>
-      <c r="C65" s="51"/>
-      <c r="D65" s="51"/>
-      <c r="E65" s="51"/>
-      <c r="F65" s="52"/>
+      <c r="A65" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="B65" s="76"/>
+      <c r="C65" s="76"/>
+      <c r="D65" s="76"/>
+      <c r="E65" s="76"/>
+      <c r="F65" s="77"/>
       <c r="G65" s="27">
         <f>I65/1.1</f>
         <v>0</v>
@@ -3159,10 +3127,10 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="77"/>
-      <c r="B66" s="37"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
+      <c r="A66" s="51"/>
+      <c r="B66" s="52"/>
+      <c r="C66" s="52"/>
+      <c r="D66" s="52"/>
       <c r="E66" s="18"/>
       <c r="F66" s="18"/>
       <c r="G66" s="19"/>
@@ -3170,125 +3138,88 @@
       <c r="I66" s="20"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A67" s="39" t="s">
+      <c r="A67" s="67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" s="68"/>
+      <c r="C67" s="68"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="68"/>
+      <c r="F67" s="68"/>
+      <c r="G67" s="68"/>
+      <c r="H67" s="68"/>
+      <c r="I67" s="69"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A68" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="36"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="36"/>
+      <c r="G68" s="36"/>
+      <c r="H68" s="36"/>
+      <c r="I68" s="37"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A69" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="B69" s="36"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="36"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="36"/>
+      <c r="G69" s="36"/>
+      <c r="H69" s="36"/>
+      <c r="I69" s="37"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A70" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="36"/>
+      <c r="G70" s="36"/>
+      <c r="H70" s="36"/>
+      <c r="I70" s="37"/>
+    </row>
+    <row r="71" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B67" s="40"/>
-      <c r="C67" s="40"/>
-      <c r="D67" s="40"/>
-      <c r="E67" s="40"/>
-      <c r="F67" s="40"/>
-      <c r="G67" s="40"/>
-      <c r="H67" s="40"/>
-      <c r="I67" s="41"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A68" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="B68" s="58"/>
-      <c r="C68" s="58"/>
-      <c r="D68" s="58"/>
-      <c r="E68" s="58"/>
-      <c r="F68" s="58"/>
-      <c r="G68" s="58"/>
-      <c r="H68" s="58"/>
-      <c r="I68" s="59"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A69" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="B69" s="58"/>
-      <c r="C69" s="58"/>
-      <c r="D69" s="58"/>
-      <c r="E69" s="58"/>
-      <c r="F69" s="58"/>
-      <c r="G69" s="58"/>
-      <c r="H69" s="58"/>
-      <c r="I69" s="59"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A70" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="B70" s="58"/>
-      <c r="C70" s="58"/>
-      <c r="D70" s="58"/>
-      <c r="E70" s="58"/>
-      <c r="F70" s="58"/>
-      <c r="G70" s="58"/>
-      <c r="H70" s="58"/>
-      <c r="I70" s="59"/>
-    </row>
-    <row r="71" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="63" t="s">
-        <v>23</v>
-      </c>
-      <c r="B71" s="45"/>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="45"/>
-      <c r="H71" s="45"/>
-      <c r="I71" s="46"/>
+      <c r="B71" s="60"/>
+      <c r="C71" s="60"/>
+      <c r="D71" s="60"/>
+      <c r="E71" s="60"/>
+      <c r="F71" s="60"/>
+      <c r="G71" s="60"/>
+      <c r="H71" s="60"/>
+      <c r="I71" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A71:I71"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="E4:F5"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="H8:I8"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:A64"/>
@@ -3300,22 +3231,59 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B16:D16"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="E4:F5"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A70:I70"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/견적서_template.xlsx
+++ b/templates/견적서_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DAILYCIGAR_DB\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232D9337-815C-405F-994A-8ACF7D98F02B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A852881-1374-4268-AD44-F594F2AAB2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="14892" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서_기본" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t>견 적 서</t>
   </si>
@@ -91,9 +91,6 @@
     <t xml:space="preserve"> 1) 견적 유효기간은 15일입니다.   2) 납기 조건: 재고 보유 시 2~3일 이내 발송</t>
   </si>
   <si>
-    <t xml:space="preserve"> 3) 배송비: 30만원 금액 이상 무료, 이하 실비 청구 4) 제품 상태 안내: 수입 후 숙성(Conditioning) 완료 제품만 출고</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 5) 교환/반품 정책: 수령 후 7일 이내 미개봉 제품에 한함</t>
   </si>
   <si>
@@ -105,6 +102,14 @@
   <si>
     <t xml:space="preserve">  (주)데일리시가
 아래와 같이 견적서를 보내 드립니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3) 배송비: 50만원 금액 이상 무료, 이하 실비 청구 4) 제품 상태 안내: 수입 후 숙성(Conditioning) 완료 제품만 출고</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OTHERS</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -269,7 +274,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -284,12 +289,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="44">
     <border>
       <left/>
       <right/>
@@ -784,6 +801,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -828,7 +897,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -840,33 +909,6 @@
     </xf>
     <xf numFmtId="42" fontId="6" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="0" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="15" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="0" borderId="4" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -882,52 +924,88 @@
     <xf numFmtId="42" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="27" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="16" fillId="0" borderId="27" xfId="10" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="15" fillId="0" borderId="32" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="42" fontId="13" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="14" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="4" xfId="10" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="15" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="3" borderId="4" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="16" fillId="3" borderId="4" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="15" fillId="3" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="16" fillId="3" borderId="1" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="15" fillId="3" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="3" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="3" borderId="27" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="3" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="16" fillId="3" borderId="27" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="15" fillId="3" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="4" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -950,20 +1028,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -973,6 +1054,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1007,12 +1091,32 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="42" fontId="14" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="17">
     <cellStyle name="쉼표 [0]" xfId="13" builtinId="6"/>
@@ -1416,848 +1520,848 @@
   <dimension ref="A1:I71"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" style="13" customWidth="1"/>
+    <col min="1" max="1" width="3.59765625" style="4" customWidth="1"/>
     <col min="2" max="2" width="8.3984375" customWidth="1"/>
-    <col min="3" max="3" width="29.19921875" style="13" customWidth="1"/>
-    <col min="4" max="4" width="3.3984375" style="13" customWidth="1"/>
-    <col min="5" max="5" width="4.796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.8984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.8984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="13" customWidth="1"/>
-    <col min="9" max="9" width="10.8984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.19921875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="3.3984375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="4.796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="4" customWidth="1"/>
+    <col min="9" max="9" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
     </row>
     <row r="2" spans="1:9" ht="6.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="74"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="44">
+      <c r="A3" s="47">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
-      </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="41" t="s">
+        <v>46146</v>
+      </c>
+      <c r="B3" s="48"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="48"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="51"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="26"/>
-      <c r="C4" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="42"/>
-      <c r="E4" s="33" t="s">
+      <c r="A4" s="12"/>
+      <c r="C4" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="45"/>
+      <c r="E4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="56"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="37"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="40"/>
     </row>
     <row r="5" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="14"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="37"/>
+      <c r="A5" s="5"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="40"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="14"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="38" t="s">
+      <c r="A6" s="5"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="81"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="37"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="40"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="49" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="61"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="65"/>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="32"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="13"/>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="71"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="76"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="21" t="s">
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="31"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
     </row>
     <row r="11" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="79"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="7"/>
+      <c r="A11" s="84"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="24"/>
     </row>
     <row r="12" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="79"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="7"/>
+      <c r="A12" s="84"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="24"/>
     </row>
     <row r="13" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="79"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="7"/>
+      <c r="A13" s="84"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="24"/>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="79"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="7"/>
+      <c r="A14" s="84"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="79"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="7"/>
+      <c r="A15" s="84"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="79"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="7"/>
+      <c r="A16" s="84"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="24"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="79"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="7"/>
+      <c r="A17" s="84"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="24"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="79"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="7"/>
+      <c r="A18" s="84"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="24"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="79"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="7"/>
+      <c r="A19" s="84"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="24"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="79"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="7"/>
+      <c r="A20" s="84"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="79"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="7"/>
+      <c r="A21" s="84"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="24"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="79"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="7"/>
+      <c r="A22" s="84"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="24"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="79"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="7"/>
+      <c r="A23" s="84"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="24"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="79"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="7"/>
+      <c r="A24" s="84"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="24"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="79"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="7"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="24"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="79"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="7"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="24"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="79"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="7"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="24"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="79"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="7"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="24"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="79"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="7"/>
+      <c r="A29" s="84"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="24"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="79"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="7"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="24"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="79"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="7"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="24"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="79"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="7"/>
+      <c r="A32" s="84"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="24"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A33" s="79"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="7"/>
+      <c r="A33" s="84"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="24"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="79"/>
-      <c r="B34" s="33"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="7"/>
+      <c r="A34" s="84"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="24"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A35" s="79"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="7"/>
+      <c r="A35" s="84"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="24"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A36" s="79"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="7"/>
+      <c r="A36" s="84"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="24"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A37" s="79"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="7"/>
+      <c r="A37" s="84"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="24"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="79"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="7"/>
+      <c r="A38" s="84"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="24"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="79"/>
-      <c r="B39" s="33"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="7"/>
+      <c r="A39" s="84"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="24"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A40" s="79"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="7"/>
+      <c r="A40" s="84"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="24"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A41" s="79"/>
-      <c r="B41" s="33"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="7"/>
+      <c r="A41" s="84"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="24"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A42" s="79"/>
-      <c r="B42" s="33"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="7"/>
+      <c r="A42" s="84"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="24"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A43" s="79"/>
-      <c r="B43" s="33"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="7"/>
+      <c r="A43" s="84"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="24"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A44" s="79"/>
-      <c r="B44" s="33"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="7"/>
+      <c r="A44" s="84"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="24"/>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="79"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="7"/>
+      <c r="A45" s="84"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="24"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A46" s="79"/>
-      <c r="B46" s="38"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="7"/>
+      <c r="A46" s="84"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="24"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A47" s="79"/>
-      <c r="B47" s="38"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="7"/>
+      <c r="A47" s="84"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="23"/>
+      <c r="I47" s="24"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A48" s="79"/>
-      <c r="B48" s="38"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="7"/>
+      <c r="A48" s="84"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="23"/>
+      <c r="I48" s="24"/>
     </row>
     <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="79"/>
-      <c r="B49" s="38"/>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="7"/>
+      <c r="A49" s="84"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="24"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A50" s="79"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="34"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="7"/>
+      <c r="A50" s="84"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="24"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A51" s="79"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="34"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="7"/>
+      <c r="A51" s="84"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="23"/>
+      <c r="I51" s="24"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A52" s="79"/>
-      <c r="B52" s="33"/>
-      <c r="C52" s="34"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="7"/>
+      <c r="A52" s="84"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="24"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A53" s="79"/>
-      <c r="B53" s="33"/>
-      <c r="C53" s="34"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="7"/>
+      <c r="A53" s="84"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="23"/>
+      <c r="I53" s="24"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A54" s="79"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="34"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="7"/>
+      <c r="A54" s="84"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="37"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="24"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A55" s="79"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="34"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="7"/>
+      <c r="A55" s="84"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="23"/>
+      <c r="I55" s="24"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A56" s="79"/>
-      <c r="B56" s="33"/>
-      <c r="C56" s="34"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="7"/>
+      <c r="A56" s="84"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="24"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A57" s="79"/>
-      <c r="B57" s="33"/>
-      <c r="C57" s="34"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="7"/>
+      <c r="A57" s="84"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="37"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="23"/>
+      <c r="I57" s="24"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A58" s="79"/>
-      <c r="B58" s="33"/>
-      <c r="C58" s="34"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="7"/>
+      <c r="A58" s="84"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="23"/>
+      <c r="I58" s="24"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A59" s="79"/>
-      <c r="B59" s="33"/>
-      <c r="C59" s="34"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="7"/>
+      <c r="A59" s="84"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="31"/>
+      <c r="H59" s="23"/>
+      <c r="I59" s="24"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A60" s="79"/>
-      <c r="B60" s="33"/>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="7"/>
+      <c r="A60" s="84"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="31"/>
+      <c r="H60" s="23"/>
+      <c r="I60" s="24"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A61" s="79"/>
-      <c r="B61" s="33"/>
-      <c r="C61" s="34"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="7"/>
+      <c r="A61" s="84"/>
+      <c r="B61" s="36"/>
+      <c r="C61" s="37"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="23"/>
+      <c r="I61" s="24"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A62" s="79"/>
-      <c r="B62" s="33"/>
-      <c r="C62" s="34"/>
-      <c r="D62" s="34"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="7"/>
+      <c r="A62" s="84"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="37"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="31"/>
+      <c r="H62" s="23"/>
+      <c r="I62" s="24"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A63" s="79"/>
-      <c r="B63" s="33"/>
-      <c r="C63" s="34"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="7"/>
+      <c r="A63" s="84"/>
+      <c r="B63" s="36"/>
+      <c r="C63" s="37"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="31"/>
+      <c r="H63" s="23"/>
+      <c r="I63" s="24"/>
     </row>
     <row r="64" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="80"/>
-      <c r="B64" s="49"/>
-      <c r="C64" s="50"/>
-      <c r="D64" s="50"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="24"/>
-      <c r="I64" s="25"/>
+      <c r="A64" s="85"/>
+      <c r="B64" s="52"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="53"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="29"/>
     </row>
     <row r="65" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="75" t="s">
+      <c r="A65" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="B65" s="76"/>
-      <c r="C65" s="76"/>
-      <c r="D65" s="76"/>
-      <c r="E65" s="76"/>
-      <c r="F65" s="77"/>
-      <c r="G65" s="27">
+      <c r="B65" s="81"/>
+      <c r="C65" s="81"/>
+      <c r="D65" s="81"/>
+      <c r="E65" s="81"/>
+      <c r="F65" s="82"/>
+      <c r="G65" s="93">
         <f>I65/1.1</f>
         <v>0</v>
       </c>
-      <c r="H65" s="28">
+      <c r="H65" s="92">
         <f t="shared" ref="H65" si="0">G65*0.1</f>
         <v>0</v>
       </c>
-      <c r="I65" s="29">
+      <c r="I65" s="91">
         <f>SUM(I10:I64)</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="51"/>
-      <c r="B66" s="52"/>
-      <c r="C66" s="52"/>
-      <c r="D66" s="52"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="20"/>
+      <c r="A66" s="54"/>
+      <c r="B66" s="55"/>
+      <c r="C66" s="55"/>
+      <c r="D66" s="55"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="10"/>
+      <c r="I66" s="11"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A67" s="67" t="s">
+      <c r="A67" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="B67" s="68"/>
-      <c r="C67" s="68"/>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
-      <c r="H67" s="68"/>
-      <c r="I67" s="69"/>
+      <c r="B67" s="73"/>
+      <c r="C67" s="73"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="73"/>
+      <c r="F67" s="73"/>
+      <c r="G67" s="73"/>
+      <c r="H67" s="73"/>
+      <c r="I67" s="74"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A68" s="40" t="s">
+      <c r="A68" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B68" s="39"/>
+      <c r="C68" s="39"/>
+      <c r="D68" s="39"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="39"/>
+      <c r="H68" s="39"/>
+      <c r="I68" s="40"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A69" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
-      <c r="F68" s="36"/>
-      <c r="G68" s="36"/>
-      <c r="H68" s="36"/>
-      <c r="I68" s="37"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A69" s="40" t="s">
+      <c r="B69" s="39"/>
+      <c r="C69" s="39"/>
+      <c r="D69" s="39"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="39"/>
+      <c r="H69" s="39"/>
+      <c r="I69" s="40"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A70" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B69" s="36"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="36"/>
-      <c r="H69" s="36"/>
-      <c r="I69" s="37"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A70" s="40" t="s">
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39"/>
+      <c r="I70" s="40"/>
+    </row>
+    <row r="71" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="36"/>
-      <c r="I70" s="37"/>
-    </row>
-    <row r="71" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="59" t="s">
-        <v>19</v>
-      </c>
-      <c r="B71" s="60"/>
-      <c r="C71" s="60"/>
-      <c r="D71" s="60"/>
-      <c r="E71" s="60"/>
-      <c r="F71" s="60"/>
-      <c r="G71" s="60"/>
-      <c r="H71" s="60"/>
-      <c r="I71" s="61"/>
+      <c r="B71" s="64"/>
+      <c r="C71" s="64"/>
+      <c r="D71" s="64"/>
+      <c r="E71" s="64"/>
+      <c r="F71" s="64"/>
+      <c r="G71" s="64"/>
+      <c r="H71" s="64"/>
+      <c r="I71" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="80">
@@ -2359,848 +2463,848 @@
   <dimension ref="A1:I71"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" style="13" customWidth="1"/>
+    <col min="1" max="1" width="3.59765625" style="4" customWidth="1"/>
     <col min="2" max="2" width="8.3984375" customWidth="1"/>
-    <col min="3" max="3" width="29.19921875" style="13" customWidth="1"/>
-    <col min="4" max="4" width="3.3984375" style="13" customWidth="1"/>
-    <col min="5" max="5" width="4.796875" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.8984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.8984375" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5" style="13" customWidth="1"/>
-    <col min="9" max="9" width="10.8984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.19921875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="3.3984375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="4.796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="4" customWidth="1"/>
+    <col min="9" max="9" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
     </row>
     <row r="2" spans="1:9" ht="6.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="74"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
     </row>
     <row r="3" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="44">
+      <c r="A3" s="47">
         <f ca="1">TODAY()</f>
-        <v>46111</v>
-      </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="41" t="s">
+        <v>46146</v>
+      </c>
+      <c r="B3" s="48"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="48"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="51"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="26"/>
-      <c r="C4" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="42"/>
-      <c r="E4" s="33" t="s">
+      <c r="A4" s="12"/>
+      <c r="C4" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="45"/>
+      <c r="E4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="56"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="37"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="40"/>
     </row>
     <row r="5" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="14"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="37"/>
+      <c r="A5" s="5"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="40"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="14"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="38" t="s">
+      <c r="A6" s="5"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="81"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="37"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="40"/>
     </row>
     <row r="7" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="49" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="61"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="65"/>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="32"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="13"/>
       <c r="E8" s="3"/>
       <c r="F8" s="2"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="71"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="76"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="21" t="s">
+      <c r="B9" s="89"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="35" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="78" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="31"/>
+      <c r="A10" s="83" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="56"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
     </row>
     <row r="11" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="79"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="7"/>
+      <c r="A11" s="84"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="24"/>
     </row>
     <row r="12" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="79"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="7"/>
+      <c r="A12" s="84"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="24"/>
     </row>
     <row r="13" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="79"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="7"/>
+      <c r="A13" s="84"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="24"/>
     </row>
     <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="79"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="7"/>
+      <c r="A14" s="84"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="79"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="7"/>
+      <c r="A15" s="84"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="79"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="7"/>
+      <c r="A16" s="84"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="24"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="79"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="7"/>
+      <c r="A17" s="84"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="24"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A18" s="79"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="7"/>
+      <c r="A18" s="84"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="24"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="79"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="7"/>
+      <c r="A19" s="84"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="24"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="79"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="7"/>
+      <c r="A20" s="84"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="79"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="7"/>
+      <c r="A21" s="84"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="24"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A22" s="79"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="7"/>
+      <c r="A22" s="84"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="24"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="79"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="7"/>
+      <c r="A23" s="84"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="24"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A24" s="79"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="7"/>
+      <c r="A24" s="84"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="24"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A25" s="79"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="7"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="24"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A26" s="79"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="7"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="24"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A27" s="79"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="7"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="24"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A28" s="79"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="7"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="36"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="24"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="79"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="7"/>
+      <c r="A29" s="84"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="24"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="79"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="7"/>
+      <c r="A30" s="84"/>
+      <c r="B30" s="36"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="24"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A31" s="79"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="7"/>
+      <c r="A31" s="84"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="24"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A32" s="79"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="7"/>
+      <c r="A32" s="84"/>
+      <c r="B32" s="36"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="24"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A33" s="79"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="7"/>
+      <c r="A33" s="84"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="24"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A34" s="79"/>
-      <c r="B34" s="33"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="7"/>
+      <c r="A34" s="84"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="24"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A35" s="79"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="7"/>
+      <c r="A35" s="84"/>
+      <c r="B35" s="36"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="24"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A36" s="79"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="7"/>
+      <c r="A36" s="84"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="24"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A37" s="79"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="7"/>
+      <c r="A37" s="84"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="24"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A38" s="79"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="7"/>
+      <c r="A38" s="84"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="24"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A39" s="79"/>
-      <c r="B39" s="33"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="7"/>
+      <c r="A39" s="84"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="24"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A40" s="79"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="7"/>
+      <c r="A40" s="84"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="24"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A41" s="79"/>
-      <c r="B41" s="33"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="7"/>
+      <c r="A41" s="84"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="24"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A42" s="79"/>
-      <c r="B42" s="33"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="7"/>
+      <c r="A42" s="84"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="24"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A43" s="79"/>
-      <c r="B43" s="33"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="7"/>
+      <c r="A43" s="84"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="24"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A44" s="79"/>
-      <c r="B44" s="33"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="7"/>
+      <c r="A44" s="84"/>
+      <c r="B44" s="36"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="24"/>
     </row>
     <row r="45" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="79"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="7"/>
+      <c r="A45" s="84"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="24"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A46" s="79"/>
-      <c r="B46" s="38"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="7"/>
+      <c r="A46" s="84"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="24"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A47" s="79"/>
-      <c r="B47" s="38"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="7"/>
+      <c r="A47" s="84"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="23"/>
+      <c r="I47" s="24"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A48" s="79"/>
-      <c r="B48" s="38"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="7"/>
+      <c r="A48" s="84"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="23"/>
+      <c r="I48" s="24"/>
     </row>
     <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="79"/>
-      <c r="B49" s="38"/>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="7"/>
+      <c r="A49" s="84"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="24"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A50" s="79"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="34"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="7"/>
+      <c r="A50" s="84"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="37"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="24"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A51" s="79"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="34"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="7"/>
+      <c r="A51" s="84"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="23"/>
+      <c r="I51" s="24"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A52" s="79"/>
-      <c r="B52" s="33"/>
-      <c r="C52" s="34"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="7"/>
+      <c r="A52" s="84"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="24"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A53" s="79"/>
-      <c r="B53" s="33"/>
-      <c r="C53" s="34"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="7"/>
+      <c r="A53" s="84"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="23"/>
+      <c r="I53" s="24"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A54" s="79"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="34"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="7"/>
+      <c r="A54" s="84"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="37"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="24"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A55" s="79"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="34"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="7"/>
+      <c r="A55" s="84"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="23"/>
+      <c r="I55" s="24"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A56" s="79"/>
-      <c r="B56" s="33"/>
-      <c r="C56" s="34"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="7"/>
+      <c r="A56" s="84"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="24"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A57" s="79"/>
-      <c r="B57" s="33"/>
-      <c r="C57" s="34"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="7"/>
+      <c r="A57" s="84"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="37"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="23"/>
+      <c r="I57" s="24"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A58" s="79"/>
-      <c r="B58" s="33"/>
-      <c r="C58" s="34"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="7"/>
+      <c r="A58" s="84"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="23"/>
+      <c r="I58" s="24"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A59" s="79"/>
-      <c r="B59" s="33"/>
-      <c r="C59" s="34"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="7"/>
+      <c r="A59" s="84"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="31"/>
+      <c r="H59" s="23"/>
+      <c r="I59" s="24"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A60" s="79"/>
-      <c r="B60" s="33"/>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="7"/>
+      <c r="A60" s="84"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="31"/>
+      <c r="H60" s="23"/>
+      <c r="I60" s="24"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A61" s="79"/>
-      <c r="B61" s="33"/>
-      <c r="C61" s="34"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="7"/>
+      <c r="A61" s="84"/>
+      <c r="B61" s="36"/>
+      <c r="C61" s="37"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="23"/>
+      <c r="I61" s="24"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A62" s="79"/>
-      <c r="B62" s="33"/>
-      <c r="C62" s="34"/>
-      <c r="D62" s="34"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="7"/>
+      <c r="A62" s="84"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="37"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="31"/>
+      <c r="H62" s="23"/>
+      <c r="I62" s="24"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A63" s="79"/>
-      <c r="B63" s="33"/>
-      <c r="C63" s="34"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="7"/>
+      <c r="A63" s="84"/>
+      <c r="B63" s="36"/>
+      <c r="C63" s="37"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="31"/>
+      <c r="H63" s="23"/>
+      <c r="I63" s="24"/>
     </row>
     <row r="64" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="80"/>
-      <c r="B64" s="49"/>
-      <c r="C64" s="50"/>
-      <c r="D64" s="50"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="24"/>
-      <c r="I64" s="25"/>
+      <c r="A64" s="85"/>
+      <c r="B64" s="52"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="53"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="29"/>
     </row>
     <row r="65" spans="1:9" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="75" t="s">
+      <c r="A65" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="B65" s="76"/>
-      <c r="C65" s="76"/>
-      <c r="D65" s="76"/>
-      <c r="E65" s="76"/>
-      <c r="F65" s="77"/>
-      <c r="G65" s="27">
+      <c r="B65" s="81"/>
+      <c r="C65" s="81"/>
+      <c r="D65" s="81"/>
+      <c r="E65" s="81"/>
+      <c r="F65" s="82"/>
+      <c r="G65" s="93">
         <f>I65/1.1</f>
         <v>0</v>
       </c>
-      <c r="H65" s="28">
+      <c r="H65" s="92">
         <f t="shared" ref="H65" si="0">G65*0.1</f>
         <v>0</v>
       </c>
-      <c r="I65" s="29">
+      <c r="I65" s="94">
         <f>SUM(I10:I64)</f>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="51"/>
-      <c r="B66" s="52"/>
-      <c r="C66" s="52"/>
-      <c r="D66" s="52"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="20"/>
+      <c r="A66" s="54"/>
+      <c r="B66" s="55"/>
+      <c r="C66" s="55"/>
+      <c r="D66" s="55"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="10"/>
+      <c r="I66" s="11"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A67" s="67" t="s">
+      <c r="A67" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="B67" s="68"/>
-      <c r="C67" s="68"/>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
-      <c r="H67" s="68"/>
-      <c r="I67" s="69"/>
+      <c r="B67" s="73"/>
+      <c r="C67" s="73"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="73"/>
+      <c r="F67" s="73"/>
+      <c r="G67" s="73"/>
+      <c r="H67" s="73"/>
+      <c r="I67" s="74"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A68" s="40" t="s">
+      <c r="A68" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B68" s="39"/>
+      <c r="C68" s="39"/>
+      <c r="D68" s="39"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="39"/>
+      <c r="H68" s="39"/>
+      <c r="I68" s="40"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A69" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
-      <c r="F68" s="36"/>
-      <c r="G68" s="36"/>
-      <c r="H68" s="36"/>
-      <c r="I68" s="37"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A69" s="40" t="s">
+      <c r="B69" s="39"/>
+      <c r="C69" s="39"/>
+      <c r="D69" s="39"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="39"/>
+      <c r="H69" s="39"/>
+      <c r="I69" s="40"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A70" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B69" s="36"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="36"/>
-      <c r="H69" s="36"/>
-      <c r="I69" s="37"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A70" s="40" t="s">
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39"/>
+      <c r="I70" s="40"/>
+    </row>
+    <row r="71" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="36"/>
-      <c r="I70" s="37"/>
-    </row>
-    <row r="71" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="59" t="s">
-        <v>19</v>
-      </c>
-      <c r="B71" s="60"/>
-      <c r="C71" s="60"/>
-      <c r="D71" s="60"/>
-      <c r="E71" s="60"/>
-      <c r="F71" s="60"/>
-      <c r="G71" s="60"/>
-      <c r="H71" s="60"/>
-      <c r="I71" s="61"/>
+      <c r="B71" s="64"/>
+      <c r="C71" s="64"/>
+      <c r="D71" s="64"/>
+      <c r="E71" s="64"/>
+      <c r="F71" s="64"/>
+      <c r="G71" s="64"/>
+      <c r="H71" s="64"/>
+      <c r="I71" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="80">
